--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_chromium/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_chromium/harmonized.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L302"/>
+  <dimension ref="A1:L303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3273,7 +3273,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3394,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3498,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3585,7 +3585,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3654,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3689,7 +3689,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3862,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4313,7 +4313,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4538,12 +4538,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4590,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4746,12 +4746,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4833,7 +4833,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5058,12 +5058,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5110,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5318,12 +5318,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5422,12 +5422,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5509,7 +5509,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5578,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5682,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5769,7 +5769,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5786,12 +5786,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5890,12 +5890,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5977,7 +5977,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5994,12 +5994,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6081,7 +6081,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6358,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6462,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6566,12 +6566,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6722,12 +6722,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6774,12 +6774,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6826,12 +6826,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6878,12 +6878,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6913,7 +6913,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6930,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7069,7 +7069,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7225,7 +7225,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7242,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7294,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7346,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7398,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7450,12 +7450,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7485,7 +7485,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7606,12 +7606,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7710,12 +7710,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7745,7 +7745,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7762,12 +7762,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7918,12 +7918,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7970,12 +7970,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8005,7 +8005,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8074,12 +8074,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8282,12 +8282,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8369,7 +8369,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8386,12 +8386,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8473,7 +8473,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8646,12 +8646,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8733,7 +8733,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8837,7 +8837,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8889,7 +8889,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8958,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8993,7 +8993,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9045,7 +9045,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9062,12 +9062,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9097,7 +9097,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9114,12 +9114,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9218,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9270,12 +9270,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9305,7 +9305,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9322,12 +9322,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9426,12 +9426,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9478,12 +9478,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9530,12 +9530,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9582,12 +9582,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9686,12 +9686,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9773,7 +9773,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9790,12 +9790,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9825,7 +9825,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9877,7 +9877,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9929,7 +9929,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10102,12 +10102,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10258,12 +10258,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10310,12 +10310,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10362,12 +10362,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10397,7 +10397,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10414,12 +10414,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10657,7 +10657,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10674,12 +10674,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10709,7 +10709,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10726,12 +10726,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10761,7 +10761,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10830,12 +10830,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10882,12 +10882,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10934,12 +10934,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11021,7 +11021,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11038,12 +11038,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11090,12 +11090,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11142,12 +11142,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11194,12 +11194,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11246,12 +11246,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11385,7 +11385,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11402,12 +11402,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11454,12 +11454,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11489,7 +11489,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11506,12 +11506,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11558,12 +11558,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11593,7 +11593,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11645,7 +11645,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11697,7 +11697,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11749,7 +11749,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11818,12 +11818,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11853,7 +11853,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11922,12 +11922,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11974,12 +11974,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12026,12 +12026,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12061,7 +12061,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12078,12 +12078,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12113,7 +12113,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12130,12 +12130,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12165,7 +12165,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12182,12 +12182,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12217,7 +12217,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12269,7 +12269,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12286,12 +12286,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12321,7 +12321,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12373,7 +12373,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12390,12 +12390,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12425,7 +12425,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12442,12 +12442,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12494,12 +12494,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12529,7 +12529,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12546,12 +12546,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12598,12 +12598,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12633,7 +12633,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12685,7 +12685,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12702,12 +12702,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12737,7 +12737,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12754,12 +12754,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12789,7 +12789,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12841,7 +12841,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12858,12 +12858,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12910,12 +12910,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12945,7 +12945,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12962,12 +12962,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13049,7 +13049,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13066,12 +13066,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13101,7 +13101,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13118,12 +13118,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13170,12 +13170,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13205,7 +13205,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13222,12 +13222,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13274,12 +13274,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13309,7 +13309,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13326,12 +13326,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13361,7 +13361,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13413,7 +13413,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13430,12 +13430,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13465,7 +13465,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13482,12 +13482,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13517,7 +13517,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13534,12 +13534,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13569,7 +13569,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13586,12 +13586,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13621,7 +13621,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13638,12 +13638,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13673,7 +13673,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13742,12 +13742,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13777,7 +13777,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13794,12 +13794,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13829,7 +13829,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13846,12 +13846,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13881,7 +13881,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13898,12 +13898,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13933,7 +13933,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13950,12 +13950,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13985,7 +13985,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14002,12 +14002,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14054,12 +14054,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14089,7 +14089,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14106,12 +14106,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14141,7 +14141,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14193,7 +14193,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14210,12 +14210,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14245,7 +14245,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14262,12 +14262,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14297,7 +14297,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14314,12 +14314,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14349,7 +14349,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14366,12 +14366,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14401,7 +14401,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14418,12 +14418,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14453,7 +14453,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14470,17 +14470,17 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
@@ -14505,7 +14505,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14522,17 +14522,17 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
@@ -14557,7 +14557,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14574,17 +14574,17 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
@@ -14609,7 +14609,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14626,17 +14626,17 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -14661,7 +14661,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14678,17 +14678,17 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -14713,7 +14713,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14730,17 +14730,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -14765,7 +14765,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14782,17 +14782,17 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
@@ -14817,7 +14817,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14834,17 +14834,17 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14886,17 +14886,17 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14938,17 +14938,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14990,17 +14990,17 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15042,17 +15042,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15094,17 +15094,17 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15146,17 +15146,17 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15198,17 +15198,17 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>-300--250</t>
+          <t>-250--200</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15250,17 +15250,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>10-20</t>
+          <t>-300--250</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15302,17 +15302,17 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>10-20</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15354,17 +15354,17 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>-10-0</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -15389,7 +15389,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15406,17 +15406,17 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>-20--10</t>
+          <t>-10-0</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15458,17 +15458,17 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>-30--20</t>
+          <t>-20--10</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -15493,7 +15493,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15510,17 +15510,17 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>-40--30</t>
+          <t>-30--20</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15562,17 +15562,17 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>-50--40</t>
+          <t>-40--30</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15614,17 +15614,17 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>-60--50</t>
+          <t>-50--40</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
@@ -15633,7 +15633,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15666,17 +15666,17 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>-70--60</t>
+          <t>-60--50</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15718,17 +15718,17 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>-80--70</t>
+          <t>-70--60</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
@@ -15737,7 +15737,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15770,17 +15770,17 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>-90--80</t>
+          <t>-80--70</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
@@ -15789,7 +15789,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15822,17 +15822,17 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>-100--90</t>
+          <t>-90--80</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15874,17 +15874,17 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>-125--100</t>
+          <t>-100--90</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15926,17 +15926,17 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>-150--125</t>
+          <t>-125--100</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15978,17 +15978,17 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>-175--150</t>
+          <t>-150--125</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16030,17 +16030,17 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>-200--175</t>
+          <t>-175--150</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16082,26 +16082,26 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>-250--200</t>
+          <t>-200--175</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>2011-12-15</t>
+          <t>2012-08-15</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>30.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -16117,7 +16117,59 @@
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>doi:10.3334/CDIAC/SPRUCE.005</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Peat_Characteristics_T0_20180425.csv</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Ho:21:-250--200</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Topography:Plot:depth</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>-250--200</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>2011-12-15</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>47.5056</v>
+      </c>
+      <c r="J303" t="n">
+        <v>-93.45328000000001</v>
+      </c>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Cr (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
